--- a/entregables/recuperacion_por_fuente_fen.xlsx
+++ b/entregables/recuperacion_por_fuente_fen.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +46,9 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <color rgb="00777777"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -61,12 +64,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00D9EAD3"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,20 +109,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -137,8 +140,23 @@
     <xf numFmtId="2" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -505,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -515,20 +533,20 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RESUMEN - rec_d por fuente (cada hoja trae el calculo detallado)</t>
+          <t>RESUMEN - rec_d por fuente, 25 departamentos (cada hoja trae el calculo detallado)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mismo depto salta de 0,25 a 1,00 segun la fuente -&gt; no hay valor robusto -&gt; FINAL 0,50 (medio conservador). El DANO ya esta en el score R.</t>
+          <t>En los 5 golpeados el mismo depto salta de 0,25 a 1,00 segun la fuente -&gt; no hay valor robusto -&gt; FINAL 0,50. Los 20 restantes = 1,00 (sin shock FEN). El DANO ya esta en el score R.</t>
         </is>
       </c>
     </row>
@@ -570,7 +588,7 @@
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>Por que 0,50</t>
+          <t>Por que</t>
         </is>
       </c>
     </row>
@@ -734,21 +752,661 @@
       </c>
       <c r="H8" s="9" t="inlineStr">
         <is>
-          <t>IBK+ mixto (minería), resto recupero -&gt; 0,50.</t>
+          <t>IBK+ mixto (mineria), resto recupero -&gt; 0,50.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>Costa centro, sin dano FEN economico (huaicos localizados Chosica) -&gt; sin shock FEN -&gt; 1,00</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Fuentes: IBK+ consumo Intercorp | BCRP/Macroconsult PBI 2024 | MIDAGRI agro 2024 | INEI IPC. Uso: originacion/pricing.</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>Costa centro, sin dano FEN -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Ica</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Costa sur, no epicentro FEN (inflacion ~0) -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Arequipa</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Moquegua</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Tacna</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Cajamarca</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>Interior, fuera del gate Pacifico -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
+        <is>
+          <t>Interior / selva -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Apurimac</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Ayacucho</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Cusco</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra sur -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Huancavelica</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Huanuco</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
+        <is>
+          <t>Interior -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Junin</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra central -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Loreto</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Madre de Dios</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Pasco</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Puno</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
+        <is>
+          <t>Altiplano -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>San Martin</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Ucayali</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="14" t="inlineStr">
+        <is>
+          <t>1,00</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Fuentes: IBK+ consumo Intercorp | BCRP/Macroconsult PBI 2024 | MIDAGRI agro 2024 | INEI IPC. Uso: originacion/pricing, no ECL.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -761,14 +1419,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,27 +1445,32 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Metrica (dato Yaku)</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Recuperacion % (metrica)</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>rec_d (redondeo)</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Como se llega</t>
         </is>
@@ -815,25 +1479,30 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>La Libertad</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>nivel 2,03 -&gt; 1,91</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>1,91/2,03 = 94% -&gt; 0,94 mas cerca de 1,00</t>
+          <t>Piura</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>nivel 2,01 -&gt; 1,55</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>1,55/2,01 = 77% -&gt; 0,77 mas cerca de 0,75</t>
         </is>
       </c>
     </row>
@@ -843,20 +1512,25 @@
           <t>Lambayeque</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>nivel 0,78 -&gt; 1,67</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>1,67/0,78 = 214% -&gt; cap 100% -&gt; 1,00</t>
         </is>
@@ -865,92 +1539,707 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Piura</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>nivel 2,01 -&gt; 1,55</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>1,55/2,01 = 77% -&gt; 0,77 mas cerca de 0,75</t>
+          <t>La Libertad</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>nivel 2,03 -&gt; 1,91</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>1,91/2,03 = 94% -&gt; 0,94 mas cerca de 1,00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ancash</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>nivel 1,80 -&gt; 0,78</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>43%</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>0,78/1,80 = 43% -&gt; 0,43 mas cerca de 0,50</t>
+          <t>Tumbes</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>sin serie Intercorp</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Intercorp no opera en Tumbes -&gt; s/d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Tumbes</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>sin serie Intercorp</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>s/d</t>
+          <t>Ancash</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>nivel 1,80 -&gt; 0,78</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>s/d</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Intercorp no opera en Tumbes -&gt; s/d</t>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="E8" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>0,78/1,80 = 43% -&gt; 0,43 mas cerca de 0,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Costa centro, sin dano FEN economico (huaicos localizados Chosica) -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Resto 20 deptos: no golpeados / interior -&gt; rec_d = 1,00.</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Costa centro, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Ica</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Costa sur, no epicentro FEN (inflacion ~0) -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Arequipa</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Moquegua</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Tacna</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Cajamarca</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Interior, fuera del gate Pacifico -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Interior / selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Apurimac</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Ayacucho</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Cusco</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra sur -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Huancavelica</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Huanuco</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Interior -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Junin</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra central -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Loreto</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Madre de Dios</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Pasco</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Puno</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Altiplano -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>San Martin</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Ucayali</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Los 20 no golpeados = 1,00 en TODAS las fuentes: el overlay solo aplica a costa expuesta (gate Pacifico), no tienen caida FEN que recuperar.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -962,14 +2251,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -987,27 +2277,32 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Metrica (dato Yaku)</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Recuperacion % (metrica)</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>rec_d (redondeo)</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Como se llega</t>
         </is>
@@ -1019,20 +2314,25 @@
           <t>Piura</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>+3,3% (Talara)</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>50+3,3x16,7 = 105% -&gt; cap -&gt; 1,00 (ojo: por petroleo, no FEN)</t>
         </is>
@@ -1041,115 +2341,735 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Ancash</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>+2,5%</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>50+2,5x16,7 = 92% -&gt; 0,92 mas cerca de 1,00</t>
+          <t>Lambayeque</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>-5,7% (aun cae)</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>5%</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>50-5,7x16,7 &lt; 0% -&gt; 0,25 (piso)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Tumbes</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>+0,1%</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
-      </c>
-      <c r="D6" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>50+0,1x16,7 = 52% -&gt; 0,52 mas cerca de 0,50</t>
+          <t>La Libertad</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>-2,4% (aun cae)</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>10%</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>50-2,4x16,7 = 10% -&gt; mas cerca de 0,25 (piso)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>La Libertad</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>-2,4% (aun cae)</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>50-2,4x16,7 = 10% -&gt; mas cerca de 0,25 (piso)</t>
+          <t>Tumbes</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>+0,1%</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>50+0,1x16,7 = 52% -&gt; 0,52 mas cerca de 0,50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Lambayeque</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>-5,7% (aun cae)</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>5%</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>50-5,7x16,7 &lt; 0% -&gt; 0,25 (piso)</t>
+          <t>Ancash</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>+2,5%</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>92%</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>50+2,5x16,7 = 92% -&gt; 0,92 mas cerca de 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Costa centro, sin dano FEN economico (huaicos localizados Chosica) -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Resto 20 deptos: no golpeados / interior -&gt; rec_d = 1,00.</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Costa centro, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Ica</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Costa sur, no epicentro FEN (inflacion ~0) -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Arequipa</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Moquegua</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Tacna</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Cajamarca</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Interior, fuera del gate Pacifico -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Interior / selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Apurimac</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Ayacucho</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Cusco</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra sur -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Huancavelica</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Huanuco</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Interior -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Junin</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra central -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Loreto</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Madre de Dios</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Pasco</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Puno</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Altiplano -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>San Martin</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Ucayali</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Los 20 no golpeados = 1,00 en TODAS las fuentes: el overlay solo aplica a costa expuesta (gate Pacifico), no tienen caida FEN que recuperar.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1161,14 +3081,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1186,27 +3107,32 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Metrica (dato Yaku)</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Recuperacion % (metrica)</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>rec_d (redondeo)</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Como se llega</t>
         </is>
@@ -1218,139 +3144,764 @@
           <t>Piura</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>mango +433%, uva, arroz</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Agro volvio/supero el nivel pre-Yaku -&gt; ~100% -&gt; 1,00</t>
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>Agro volvio/supero nivel pre-Yaku -&gt; ~100% -&gt; 1,00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>La Libertad</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>arandano +100%</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
+          <t>Lambayeque</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>arandano/uva; arroz +5,9%</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>Agroexport recupero -&gt; ~100% -&gt; 1,00</t>
+      <c r="E5" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>Agro recupero -&gt; ~100% -&gt; 1,00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Lambayeque</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>arandano/uva; arroz +5,9%</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
+          <t>La Libertad</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>arandano +100%</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Agro recupero -&gt; ~100% -&gt; 1,00</t>
+      <c r="E6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>Agroexport recupero -&gt; ~100% -&gt; 1,00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ancash</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>agro +12,8% (tras -9,9% 2023)</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Neto ~+2% vs pre -&gt; ~100% -&gt; 1,00</t>
+          <t>Tumbes</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>banano/langostino (s/d)</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>s/d</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Sin dato desagregado -&gt; s/d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Tumbes</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>banano/langostino (s/d)</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>s/d</t>
+          <t>Ancash</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>agro +12,8% (tras -9,9% 2023)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>s/d</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Sin dato desagregado -&gt; s/d</t>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Neto ~+2% vs pre -&gt; ~100% -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Costa centro, sin dano FEN economico (huaicos localizados Chosica) -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Resto 20 deptos: no golpeados / interior -&gt; rec_d = 1,00.</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Costa centro, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Ica</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Costa sur, no epicentro FEN (inflacion ~0) -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Arequipa</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Moquegua</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Tacna</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Cajamarca</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Interior, fuera del gate Pacifico -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Interior / selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Apurimac</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Ayacucho</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Cusco</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra sur -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Huancavelica</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Huanuco</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Interior -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Junin</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra central -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Loreto</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Madre de Dios</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Pasco</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Puno</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Altiplano -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>San Martin</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Ucayali</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Los 20 no golpeados = 1,00 en TODAS las fuentes: el overlay solo aplica a costa expuesta (gate Pacifico), no tienen caida FEN que recuperar.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1362,14 +3913,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1387,27 +3939,32 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Departamento</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Metrica (dato Yaku)</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>Recuperacion % (metrica)</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>rec_d (redondeo)</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Como se llega</t>
         </is>
@@ -1419,20 +3976,25 @@
           <t>Piura</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
         <is>
           <t>shock +0,66 -&gt; rev -1,64</t>
         </is>
       </c>
-      <c r="C4" s="7" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="D4" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>1,64/0,66 = 248% -&gt; cap -&gt; 1,00 (normalizo del todo)</t>
         </is>
@@ -1441,115 +4003,735 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Tumbes</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>shock +0,70 -&gt; rev -1,30</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>1,30/0,70 = 186% -&gt; cap -&gt; 1,00</t>
+          <t>Lambayeque</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>shock +1,31 -&gt; rev -0,66</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>0,66/1,31 = 50% -&gt; 0,50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Ancash</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>shock +0,50 -&gt; rev -1,18</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>1,18/0,50 = 236% -&gt; cap -&gt; 1,00</t>
+          <t>La Libertad</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>shock +2,24 -&gt; rev -1,38</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>1,38/2,24 = 62% -&gt; 0,62 mas cerca de 0,50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>La Libertad</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>shock +2,24 -&gt; rev -1,38</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>62%</t>
-        </is>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>1,38/2,24 = 62% -&gt; 0,62 mas cerca de 0,50</t>
+          <t>Tumbes</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>shock +0,70 -&gt; rev -1,30</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>1,30/0,70 = 186% -&gt; cap -&gt; 1,00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Lambayeque</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>shock +1,31 -&gt; rev -0,66</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="D8" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>0,66/1,31 = 50% -&gt; 0,50</t>
+          <t>Ancash</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Golpeado FEN</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>shock +0,50 -&gt; rev -1,18</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>1,18/0,50 = 236% -&gt; cap -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Lima</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Costa centro, sin dano FEN economico (huaicos localizados Chosica) -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Resto 20 deptos: no golpeados / interior -&gt; rec_d = 1,00.</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>Callao</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="15" t="inlineStr">
+        <is>
+          <t>Costa centro, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>Ica</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="15" t="inlineStr">
+        <is>
+          <t>Costa sur, no epicentro FEN (inflacion ~0) -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>Arequipa</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Moquegua</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Tacna</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="15" t="inlineStr">
+        <is>
+          <t>Sur, sin dano FEN -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Cajamarca</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Interior, fuera del gate Pacifico -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="15" t="inlineStr">
+        <is>
+          <t>Interior / selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>Apurimac</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Ayacucho</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Cusco</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra sur -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Huancavelica</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>Huanuco</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>Interior -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>Junin</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra central -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Loreto</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>Madre de Dios</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D24" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>Pasco</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D25" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>Interior / sierra -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Puno</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D26" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>Altiplano -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>San Martin</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Ucayali</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>No golpeado</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="D28" s="14" t="inlineStr">
+        <is>
+          <t>--</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>Selva -&gt; sin shock FEN que recuperar -&gt; 1,00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Los 20 no golpeados = 1,00 en TODAS las fuentes: el overlay solo aplica a costa expuesta (gate Pacifico), no tienen caida FEN que recuperar.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
